--- a/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A function could quietly return `None` on invalid input instead of raising. Why is raising usually the better choice?</t>
+          <t>A signup form's validation function could quietly return `None` when a user's age input is invalid, instead of alerting anything upstream. Why is raising usually the better choice?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which category of error stops Python before any code runs at all, caught by Python's own grammar check?</t>
+          <t>A developer typos a colon while writing an age-check condition in a school attendance app and Python refuses to run the file at all. Which category of error stops Python before any code runs at all, caught by Python's own grammar check?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1605,7 +1605,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age = `int(input('Enter your age: '))` raises a `ValueError` when the user types 'twenty'. What kind of error is this?</t>
+          <t>A gym membership sign-up form expects a numeric age but a user types a word instead:
+```python
+age = int(input('Enter your age: '))
+```
+This raises a `ValueError` when the user types 'twenty'. What kind of error is this?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1683,7 +1687,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>def `average(a, b)`: return a + b / 2. Calling `average(10, 20)` returns 20.0 instead of the intended 15.0, with no crash at all. What kind of error is this?</t>
+          <t>A grading tool for a school app has a bug that returns the wrong average with no crash at all:
+```python
+def average(a, b):
+    return a + b / 2
+```
+Calling `average(10, 20)` returns 20.0 instead of the intended 15.0. What kind of error is this?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1761,7 +1770,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why does exception handling specifically target runtime errors rather than syntax or logic errors?</t>
+          <t>A team lead is explaining to new hires why their bug-tracking system only wraps certain kinds of mistakes in try/except blocks. Why does exception handling specifically target runtime errors rather than syntax or logic errors?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1839,7 +1848,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why should a traceback be read starting from the bottom rather than the top?</t>
+          <t>A developer debugging a crashed payroll script opens a long traceback and isn't sure where to start reading it. Why should a traceback be read starting from the bottom rather than the top?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1917,7 +1926,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A `ZeroDivisionError` traceback points exactly at the line total / `len(numbers)`. What does it NOT tell you directly?</t>
+          <t>A developer investigating a crash in an inventory system sees a `ZeroDivisionError` traceback that points exactly at the line total / `len(numbers)`. What does it NOT tell you directly?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2081,7 +2090,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When reading a Python traceback, where is the single most useful line, naming the exact error type and message?</t>
+          <t>A developer debugging a failed checkout process on an e-commerce site is scanning a traceback for the fastest way to identify the problem. When reading a Python traceback, where is the single most useful line, naming the exact error type and message?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2514,7 +2523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>In a traceback with three stacked call blocks followed by a final error line, what does each block above the bottom line represent?</t>
+          <t>A developer debugging a multi-function crash in a hotel booking system opens a traceback showing three stacked call blocks followed by a final error line. What does each block above the bottom line represent?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2761,7 +2770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which syntax correctly catches both `ValueError` and `ZeroDivisionError` with one identical response?</t>
+          <t>A checkout script for an online store needs one identical error message whether the user enters non-numeric text or a quantity of zero. Which syntax correctly catches both `ValueError` and `ZeroDivisionError` with one identical response?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3093,7 +3102,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the correct rule for ordering multiple except clauses that have an inheritance relationship?</t>
+          <t>A developer building a payment-processing module is writing several except clauses for error types that inherit from one another. What is the correct rule for ordering multiple except clauses that have an inheritance relationship?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3616,7 +3625,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A program raises a plain `ValueError` for three genuinely different problems: a negative age, an unreasonably large age, and an empty name. What is the downside of this approach?</t>
+          <t>A signup form for an event-ticketing site raises a plain `ValueError` for three genuinely different problems: a negative age, an unreasonably large age, and an empty name. What is the downside of this approach?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3783,7 +3792,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A registration function needs to raise a different, specifically catchable error for an empty name versus an invalid age, so each can get its own tailored response. What is the best design?</t>
+          <t>A developer building a membership registration system needs to raise a different, specifically catchable error for an empty name versus an invalid age, so each can get its own tailored response. What is the best design?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3861,7 +3870,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A signup page for a fitness app checks user input like this before accepting it:
+```python
 age = input('Enter your age: ')
 if not age.isdigit():
     print('Please enter digits only.')
@@ -3946,7 +3956,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why might try/except around `int()` conversion be more robust than relying only on a `.isdigit()` condition check beforehand?</t>
+          <t>A developer building a food-delivery app's age-verification step is deciding how to validate numeric input most safely. Why might try/except around `int()` conversion be more robust than relying only on a `.isdigit()` condition check beforehand?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4024,7 +4034,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A payment calculation receives a negative amount due to what looks like a bug deep in the calling code. According to robust design principles, what is usually the better choice?</t>
+          <t>A payment calculation in a ride-sharing app's fare estimator receives a negative amount due to what looks like a bug deep in the calling code. According to robust design principles, what is usually the better choice?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4102,7 +4112,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A developer reviews a weather-data pipeline that silently swallows errors like this:
+```python
 try:
     result = some_complicated_calculation(data)
 except Exception:

--- a/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 12.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 12.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 12.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 12.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 12.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 12.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 12.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 12.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,14 +647,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>A `SyntaxError`, before any code runs</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>A logic error, after printing the wrong result</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>A `SyntaxError`, before any code runs</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>No error, this code runs fine</t>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -725,26 +725,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>except: ... try: ...</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>try: ... except `ValueError`: ...</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>catch: ... try: ...</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>except: ... try: ...</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>if `risky()`: ... else: ...</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>try: ... except `ValueError`: ...</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -803,26 +803,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>class InvalidAgeError: pass</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>def `InvalidAgeError()`: pass</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>class `InvalidAgeError(Exception)`: pass</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>def `InvalidAgeError()`: pass</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>class InvalidAgeError: pass</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>InvalidAgeError = `ValueError`</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -890,26 +890,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>`ValueError`: invalid literal</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`TypeError`: unsupported operand</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>`ZeroDivisionError`: division by zero</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>`TypeError`: unsupported operand</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>`ValueError`: invalid literal</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>`IndexError`: list index out of range</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -978,26 +978,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Number of people cannot be zero.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Neither message prints, the program crashes</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Number of people cannot be zero.</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Please enter whole numbers only.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Both messages print</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Please enter whole numbers only.</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Raising is technically always faster than simply returning a value</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Returning `None` is technically not allowed inside Python functions at all</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>raise technically and automatically logs the error to a file somewhere</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Returning `None` is technically not allowed inside Python functions at all</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Raising is technically always faster than simply returning a value</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1148,22 +1148,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>A custom exception combined with finally, with no loop involved</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A while loop, try/except for conversion, and if for the business rule</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Only a plain for loop combined with the `range()` function</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Only try/except is technically needed here, nothing else at all</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>A while loop, try/except for conversion, and if for the business rule</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>A custom exception combined with finally, with no loop involved</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Only a plain for loop combined with the `range()` function</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>The function crashes on '0' since 0 is falsy</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>The function loops through all three attempts and finally returns 30</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>The function returns immediately after 'abc' fails</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>The function crashes on '0' since 0 is falsy</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>The function loops through all three attempts and finally returns 30</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>The function returns 'abc' as a string since conversion was never required</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>No, this raises a `TypeError` because EmptyNameError is not built-in</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Yes, but only if EmptyNameError defines a special catch method</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>No, custom exceptions can only be caught by their own exact type</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Yes, but only if EmptyNameError defines a special catch method</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>No, this raises a `TypeError` because EmptyNameError is not built-in</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>finally technically and silently swallows the `ZeroDivisionError` entirely, hiding it</t>
+          <t>finally technically and silently swallows the `ZeroDivisionError` entirely, hiding it every time</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1575,26 +1575,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Import error</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Logic error</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Syntax error</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Runtime error</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Import error</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1657,26 +1657,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Syntax error</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Indentation error</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Logic error</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>Runtime error</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Syntax error</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Indentation error</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Logic error</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Type error</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Syntax error</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Runtime error</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Syntax error</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Type error</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1818,26 +1818,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Because logic errors are technically always fixed completely automatically by Python itself</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Because runtime errors happen mid-execution and can be anticipated and handled, unlike the other two</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Because syntax and logic errors technically cannot ever occur in Python</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Because logic errors are technically always fixed completely automatically</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Because runtime errors happen mid-execution and can be anticipated and handled, unlike the other two</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Because runtime errors are technically the only ones with a message at all</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1896,26 +1896,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Because the most specific, most useful information sits at the very bottom</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Because Python prints tracebacks upside down by mistake</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Because the very top line is technically always completely blank</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Because Python prints tracebacks upside down by mistake</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Because the most specific, most useful information sits at the very bottom</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Because reading top-down technically causes a second separate error</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1974,26 +1974,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>The exact line where the actual failure occurred here</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>The root cause of why the function received bad data in the first place</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>The exact type of the exception that occurred</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>The exact line where the actual failure occurred here</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>The name of the function where the failure occurred</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>The root cause of why the function received bad data in the first place</t>
+          <t>The name of the function where the failure originally occurred here</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2060,26 +2060,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Nothing is technically wrong at all, both clauses will run as expected</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>`Exception` is technically not a valid exception type in Python at all</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Nothing is technically wrong at all, both clauses will run as expected</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This code technically raises a `SyntaxError` because of the clause order used</t>
+          <t>The `ValueError` clause is unreachable because the broader `Exception` clause above it always matches first</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>The `ValueError` clause is unreachable because the broader `Exception` clause above it always matches first</t>
+          <t>This code technically raises a `SyntaxError` because of the exact clause order used here every time</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>The middle line, always</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>The very first line</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>The middle line, always</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2223,26 +2223,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>You are 20 years old.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Nothing prints</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Both messages print</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>That doesn't look like a valid number.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>You are 20 years old.</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2310,21 +2310,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>The program stops immediately with an unhandled `ValueError`</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Python silently skips the print statement</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>The program asks for input again automatically</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>The program stops immediately with an unhandled `ValueError`</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Python silently skips the print statement</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2498,21 +2498,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Invalid input, defaulting to 0. then Proceeding with age: 0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>You are twenty years old. then Proceeding with age: twenty</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Invalid input, defaulting to 0. then Proceeding with age: 0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Proceeding with age: 0 then Invalid input, defaulting to 0.</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>A completely separate, unrelated error happening entirely</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>A warning message that can safely be ignored entirely</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>A duplicate copy of the very bottom line shown</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>A warning message that can safely be ignored entirely</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>A completely separate, unrelated error happening entirely</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2655,22 +2655,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It technically makes the program run twice as slow as before every time</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It technically only ever works correctly with `ValueError`</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>It catches every kind of failure indiscriminately, potentially hiding real bugs</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>It is technically considered a syntax error in Python</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It technically only ever works correctly with `ValueError`</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It catches every kind of failure indiscriminately, potentially hiding real bugs</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It technically makes the program run twice as slow as before</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2740,26 +2740,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>'cleanup ran' prints, then the function returns 10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Only finally runs; the return value is lost</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The function returns 10 immediately and finally never runs, since return exits early</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>The function raises an error because finally cannot follow a return</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>'cleanup ran' prints, then the function returns 10</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>The function returns 10 immediately and finally never runs, since return exits early</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2818,26 +2818,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>except [`ValueError`, `ZeroDivisionError`]:</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>except `ValueError` and `ZeroDivisionError`:</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>except (`ValueError`, `ZeroDivisionError`):</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>except `ValueError` and `ZeroDivisionError`:</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>except [`ValueError`, `ZeroDivisionError`]:</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>except `ValueError`, `ZeroDivisionError`:</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2900,26 +2900,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>It re-raises the exception with a new name</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>It captures the actual exception object so its message can be read</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>It converts the exception into a string automatically and discards it</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>It renames the except block</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>It converts the exception into a string automatically and discards it</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It captures the actual exception object so its message can be read</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>It re-raises the exception with a new name</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2986,26 +2986,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Only if both try and except run</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Every single time, regardless of outcome</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Only if an exception was caught</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Only if the try block succeeded with no exception</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Every single time, regardless of outcome</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Only if an exception was caught</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Only if both try and except run</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3072,26 +3072,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It only prints if the input was valid</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>It prints in both cases, since finally always runs</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>It only prints if the input was invalid</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>It only prints if the input was valid</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>It never prints unless explicitly called</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>It prints in both cases, since finally always runs</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3150,26 +3150,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>The most specific exception types should be listed first, broad types last</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`Exception` types technically must be listed in alphabetical order</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Order technically does not matter at all in Python here</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Broad exception types should always be listed first</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Order technically does not matter at all in Python here</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>`Exception` types technically must be listed in alphabetical order</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>The most specific exception types should be listed first, broad types last</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Transaction attempt complete. then Total cost: 59.97</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Please enter valid numbers. then Transaction attempt complete.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Please enter valid numbers. only</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Please enter valid numbers. then Transaction attempt complete.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Transaction attempt complete. then Total cost: 59.97</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -3425,26 +3425,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Because it technically makes the function run without any arguments</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Because raising is required syntax for every function</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Because functions in Python cannot contain try/except</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>So the caller, not the function, can decide how to respond via try/except</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Because it makes the function run without any arguments</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Because functions in Python cannot contain try/except</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Because raising is required syntax for every function</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>It converts the `ZeroDivisionError` into a `ValueError`</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>It creates a brand new, unrelated exception</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>It converts the `ZeroDivisionError` into a `ValueError`</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3595,26 +3595,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It technically raises a `ZeroDivisionError` instead</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It technically returns the value `None` silently instead</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>It raises a `ValueError` immediately, before any division happens</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It technically raises a `ZeroDivisionError` instead</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It technically returns the value `None` silently instead</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>It technically prints a warning message and returns 0</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3673,26 +3673,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Python technically does not allow raising `ValueError` inside any function at all, under any condition</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Every different problem looks identical to the caller, since they are all the same generic exception type</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>It technically makes the entire program run significantly slower overall</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>`ValueError` technically cannot ever be raised more than once in a program</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Python technically does not allow raising `ValueError` inside a function at all</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Every different problem looks identical to the caller, since they are all the same generic exception type</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3767,21 +3767,21 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Registration failed: `None` printed instead</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Registration failed: Age must be between 0 and 120.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Nothing at all, the entire program crashes</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Registration failed: `None` printed instead</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Raise the same `ValueError` for both, with different message text only</t>
+          <t>Define one class that inherits from both problems simultaneously</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Define one class that inherits from both problems simultaneously</t>
+          <t>Raise the same `ValueError` for both problems, using only different message text</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -3926,26 +3926,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>It rejects bad input but never asks again, since there is no loop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>It technically accepts any input at all regardless of validity</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>It technically cannot detect invalid input of any kind at all</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>It rejects bad input but never asks again, since there is no loop</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>It technically raises a `SyntaxError` whenever bad input is entered</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4004,26 +4004,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>`isdigit()` is technically deprecated and no longer works at all in modern Python</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>try/except is more general, since `.isdigit()` only anticipates one specific kind of bad input</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>`isdigit()` technically cannot ever be used inside a while loop at all</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>try/except technically runs faster in absolutely every single case</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>`isdigit()` is technically deprecated and no longer works at all in Python</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>`isdigit()` technically cannot ever be used inside a while loop at all</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4082,26 +4082,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Always technically retry the calculation three separate times before giving up</t>
+          <t>Always technically retry the calculation three separate times before ever giving up</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Usually let it fail loudly, since a clear crash is more useful than hiding an unanticipated bug</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Convert it technically into a custom exception type and simply ignore it</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Always catch it silently and substitute a default of zero</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Convert it technically into a custom exception type and simply ignore it</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Usually let it fail loudly, since a clear crash is more useful than hiding an unanticipated bug</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4167,26 +4167,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It is technically always considered a syntax error in Python here</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>It technically prevents the function from ever returning any value at all, under any condition</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>It technically makes the function run permanently and noticeably slower</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It is technically always considered a syntax error in Python here</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>It can silently hide bugs, turning a loud crash into an invisible, hard-to-trace logic error later</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It technically prevents the function from ever returning a value at all</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
@@ -3377,12 +3377,12 @@
         raise ValueError('Number of people must be greater than zero.')
     return total / people
 ```
-Why does split_cost raise instead of handling the error itself?</t>
+Why does `split_cost` raise instead of handling the error itself?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The whole point of raising is that the caller, not the function itself, decides how to respond; split_cost stays simple and trustworthy, refusing bad input unconditionally, while the calling code decides what handling it gracefully actually looks like using try/except.</t>
+          <t>The whole point of raising is that the caller, not the function itself, decides how to respond; `split_cost` stays simple and trustworthy, refusing bad input unconditionally, while the calling code decides what handling it gracefully actually looks like using try/except.</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 12 - Exception Handling/Unit 12 - Exception Handling - MCQ.xlsx
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A developer investigating a crash in an inventory system sees a `ZeroDivisionError` traceback that points exactly at the line total / `len(numbers)`. What does it NOT tell you directly?</t>
+          <t>A developer investigating a crash in an inventory system sees a `ZeroDivisionError` traceback that points exactly at the line `total / len(numbers)`. What does it NOT tell you directly?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
